--- a/docs/paper/paper_tables.xlsx
+++ b/docs/paper/paper_tables.xlsx
@@ -438,7 +438,7 @@
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="24.2" customWidth="1" min="9" max="9"/>
+    <col width="31.9" customWidth="1" min="9" max="9"/>
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
@@ -547,7 +547,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>④</t>
+          <t>원본 파형 (전처리 없음)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -619,7 +619,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>가 u1000</t>
+          <t>CPU log-mel, 간격 62.5 ms (멜 32)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -679,7 +679,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>다 u800</t>
+          <t>CPU log-mel, 간격 50 ms</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -739,7 +739,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>간격 400</t>
+          <t>CPU log-mel, 간격 25 ms</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -799,7 +799,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>①′</t>
+          <t>CPU log-mel, 간격 16 ms</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -859,7 +859,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>(a)</t>
+          <t>NPU 근사 log</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -931,7 +931,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M4 CMSIS-NN</t>
+          <t>CPU 추론 (Cortex-M4F)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>CMSIS-NN (④ 가중치)</t>
+          <t>CMSIS-NN (원본 파형 (전처리 없음) 가중치)</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1025,26 +1025,26 @@
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="13.2" customWidth="1" min="8" max="8"/>
     <col width="60" customWidth="1" min="9" max="9"/>
     <col width="24.2" customWidth="1" min="10" max="10"/>
     <col width="48.40000000000001" customWidth="1" min="11" max="11"/>
     <col width="36.3" customWidth="1" min="12" max="12"/>
     <col width="16.5" customWidth="1" min="13" max="13"/>
-    <col width="27.5" customWidth="1" min="14" max="14"/>
-    <col width="25.3" customWidth="1" min="15" max="15"/>
-    <col width="19.8" customWidth="1" min="16" max="16"/>
-    <col width="19.8" customWidth="1" min="17" max="17"/>
-    <col width="50.6" customWidth="1" min="18" max="18"/>
-    <col width="48.40000000000001" customWidth="1" min="19" max="19"/>
-    <col width="18.7" customWidth="1" min="20" max="20"/>
-    <col width="14.3" customWidth="1" min="21" max="21"/>
+    <col width="34.1" customWidth="1" min="14" max="14"/>
+    <col width="34.1" customWidth="1" min="15" max="15"/>
+    <col width="34.1" customWidth="1" min="16" max="16"/>
+    <col width="34.1" customWidth="1" min="17" max="17"/>
+    <col width="28.6" customWidth="1" min="18" max="18"/>
+    <col width="40.7" customWidth="1" min="19" max="19"/>
+    <col width="20.9" customWidth="1" min="20" max="20"/>
+    <col width="20.9" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>표 2 주 결과. 데이터 v4+D, 시드 1~3 평균 ± 표준편차. 정답: 시험셋 testL-S3 (주; testL 은 부록 열), 외부 real31L. 오경보 300회/h (시험셋 배경에서 잡은 문턱값, 외부에도 같은 문턱값).</t>
+          <t>표 2 주 결과. 데이터 v4+D, 시드 1~3 평균 ± 표준편차. 정답: 시험 데이터 (주; 청취 전 정답은 부록 열), 외부 데이터 (AudioSet). 오경보 300회/h (시험 데이터 배경에서 잡은 문턱값, 외부에도 같은 문턱값).</t>
         </is>
       </c>
     </row>
@@ -1065,7 +1065,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>(a) 는 보드 미실측 — 적재·출력은 ④ 실측, 추론은 합성 사이클 ÷ CNN 클럭 (추정).</t>
+          <t>NPU 근사 log 는 보드 미실측 — 적재·출력은 원본 파형 (전처리 없음) 실측, 추론은 합성 사이클 ÷ CNN 클럭 (추정).</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>hop 대비 (%)</t>
+          <t>판단 주기 대비 (%)</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1137,32 +1137,32 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>시험셋 macro-F1 testL-S3 (주)</t>
+          <t>macro-F1 시험 데이터 (주)</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>시험셋 macro-F1 testL (부록)</t>
+          <t>macro-F1 시험 데이터 (청취 전 정답, 부록)</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>외부 F1 real31L</t>
+          <t>F1 외부 데이터 (AudioSet)</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>외부 mAP real31L</t>
+          <t>mAP 외부 데이터 (AudioSet)</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>시험셋 recall testL-S3 siren/glass/scream/dog (%)</t>
+          <t>재현율 시험 데이터 사이렌/유리/비명/개 (%)</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>외부 recall real31L siren/glass/scream/dog (%)</t>
+          <t>재현율 외부 데이터 (AudioSet) 사이렌/유리/비명/개 (%)</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -1179,7 +1179,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>④</t>
+          <t>원본 파형 (전처리 없음)</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -1284,7 +1284,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>가 u1000</t>
+          <t>CPU log-mel, 간격 62.5 ms (멜 32)</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -1389,7 +1389,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>다 u800</t>
+          <t>CPU log-mel, 간격 50 ms</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -1494,7 +1494,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>간격 400</t>
+          <t>CPU log-mel, 간격 25 ms</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -1599,7 +1599,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>①′</t>
+          <t>CPU log-mel, 간격 16 ms</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -1704,7 +1704,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>(a)</t>
+          <t>NPU 근사 log</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -1809,7 +1809,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M4 CMSIS-NN</t>
+          <t>CPU 추론 (Cortex-M4F)</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -1872,42 +1872,42 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>④ 와 같다 (같은 가중치·출력)</t>
+          <t>원본 파형 (전처리 없음) 와 같다 (같은 가중치·출력)</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>④ 와 같다 (같은 가중치·출력)</t>
+          <t>원본 파형 (전처리 없음) 와 같다 (같은 가중치·출력)</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>④ 와 같다 (같은 가중치·출력)</t>
+          <t>원본 파형 (전처리 없음) 와 같다 (같은 가중치·출력)</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>④ 와 같다 (같은 가중치·출력)</t>
+          <t>원본 파형 (전처리 없음) 와 같다 (같은 가중치·출력)</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>④ 와 같다</t>
+          <t>원본 파형 (전처리 없음) 와 같다</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>④ 와 같다</t>
+          <t>원본 파형 (전처리 없음) 와 같다</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>④ 와 같다</t>
+          <t>원본 파형 (전처리 없음) 와 같다</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>④ 와 같다</t>
+          <t>원본 파형 (전처리 없음) 와 같다</t>
         </is>
       </c>
     </row>
@@ -1927,10 +1927,10 @@
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="27.5" customWidth="1" min="3" max="3"/>
+    <col width="25.3" customWidth="1" min="3" max="3"/>
     <col width="25.3" customWidth="1" min="4" max="4"/>
     <col width="25.3" customWidth="1" min="5" max="5"/>
-    <col width="25.3" customWidth="1" min="6" max="6"/>
+    <col width="31.9" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1943,7 +1943,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>(a) 는 주 실행 (lr 0.0003 + 미세조정 스케줄) — 보조 실행은 판정에 쓰지 않는다 (STATUS.md).</t>
+          <t>NPU 근사 log 는 주 실행 (lr 0.0003 + 미세조정 스케줄) — 보조 실행은 판정에 쓰지 않는다 (STATUS.md).</t>
         </is>
       </c>
     </row>
@@ -1960,29 +1960,29 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>시험셋 macro-F1 testL-S3 (주)</t>
+          <t>macro-F1 시험 데이터 (주)</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>외부 F1 real31L</t>
+          <t>F1 외부 데이터 (AudioSet)</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>외부 mAP real31L</t>
+          <t>mAP 외부 데이터 (AudioSet)</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>시험셋 macro-F1 testL (부록)</t>
+          <t>macro-F1 시험 데이터 (청취 전 정답, 부록)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>가 u1000 − ④</t>
+          <t>CPU log-mel, 간격 62.5 ms (멜 32) − 원본 파형 (전처리 없음)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2014,7 +2014,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>다 u800 − ④</t>
+          <t>CPU log-mel, 간격 50 ms − 원본 파형 (전처리 없음)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2046,7 +2046,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>간격 400 − ①′</t>
+          <t>CPU log-mel, 간격 25 ms − CPU log-mel, 간격 16 ms</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2078,7 +2078,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>가 u1000 − (a)</t>
+          <t>CPU log-mel, 간격 62.5 ms (멜 32) − NPU 근사 log</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2110,7 +2110,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>(a) − ④</t>
+          <t>NPU 근사 log − 원본 파형 (전처리 없음)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2154,18 +2154,18 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="17.6" customWidth="1" min="3" max="3"/>
-    <col width="14.3" customWidth="1" min="4" max="4"/>
-    <col width="15.4" customWidth="1" min="5" max="5"/>
-    <col width="14.3" customWidth="1" min="6" max="6"/>
+    <col width="30.8" customWidth="1" min="2" max="2"/>
+    <col width="26.4" customWidth="1" min="3" max="3"/>
+    <col width="15.4" customWidth="1" min="4" max="4"/>
+    <col width="17.6" customWidth="1" min="5" max="5"/>
+    <col width="17.6" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>표 4 NPU 대 M4 CMSIS-NN. 같은 ④ 가중치·같은 출력 (보드 NPU 출력과 비트 일치, 1000회 불일치 0). 1000회 최악값.</t>
+          <t>표 4 NPU 추론 대 CPU 추론 (Cortex-M4F). 같은 가중치(원본 파형 (전처리 없음))·같은 출력 (보드 NPU 출력과 비트 일치, 1000회 불일치 0). 1000회 최악값.</t>
         </is>
       </c>
     </row>
@@ -2184,27 +2184,27 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>NPU ④ (ms)</t>
+          <t>NPU 추론 — 원본 파형 (전처리 없음) (ms)</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>M4 CMSIS-NN (ms)</t>
+          <t>CPU 추론 (Cortex-M4F) (ms)</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>배율 (M4 / NPU)</t>
+          <t>배율 (CPU / NPU)</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>hop 대비 NPU (%)</t>
+          <t>판단 주기 대비 NPU (%)</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>hop 대비 M4 (%)</t>
+          <t>판단 주기 대비 CPU (%)</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -2423,7 +2423,7 @@
     <col width="57.2" customWidth="1" min="9" max="9"/>
     <col width="45.1" customWidth="1" min="10" max="10"/>
     <col width="40.7" customWidth="1" min="11" max="11"/>
-    <col width="38.5" customWidth="1" min="12" max="12"/>
+    <col width="40.7" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2505,7 +2505,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>④ (NPU) &lt; M4 CMSIS-NN</t>
+          <t>원본 파형 (전처리 없음) (NPU 추론) &lt; CPU 추론 (Cortex-M4F)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2560,14 +2560,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>NPU 가 M4 소프트웨어 추론보다 에너지가 적은 조건</t>
+          <t>NPU 추론이 CPU 추론보다 에너지가 적은 조건</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>가 u1000 &lt; ④</t>
+          <t>CPU log-mel, 간격 62.5 ms (멜 32) &lt; 원본 파형 (전처리 없음)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2622,14 +2622,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>CPU 전처리 + 작은 NPU 가 원파형 NPU 보다 적은 조건</t>
+          <t>CPU 전처리 + 작은 NPU 가 원본 파형 NPU 보다 적은 조건</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>다 u800 &lt; ④</t>
+          <t>CPU log-mel, 간격 50 ms &lt; 원본 파형 (전처리 없음)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2691,7 +2691,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>간격 400 &lt; ①′</t>
+          <t>CPU log-mel, 간격 25 ms &lt; CPU log-mel, 간격 16 ms</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2753,7 +2753,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>(a) &lt; ④</t>
+          <t>NPU 근사 log &lt; 원본 파형 (전처리 없음)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>(a) 지연은 추정 (보드 미실측)</t>
+          <t>NPU 근사 log 지연은 추정 (보드 미실측)</t>
         </is>
       </c>
     </row>

--- a/docs/paper/paper_tables.xlsx
+++ b/docs/paper/paper_tables.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="table1_configs" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="table2_main" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="table3_welch" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="table4_npu_vs_cmsis" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="table5_breakeven" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="table6_listening" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table1_configs" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table2_main" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table3_welch" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table4_npu_vs_cmsis" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table5_breakeven" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table6_listening" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:P11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -619,67 +619,79 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CPU log-mel, 간격 62.5 ms (멜 32)</t>
+          <t>NPU 전처리 (Gabor 필터뱅크)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CPU 로그 멜 (증분)</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="D5" t="n">
-        <v>62.5</v>
-      </c>
-      <c r="E5" t="n">
-        <v>512</v>
-      </c>
-      <c r="F5" t="n">
-        <v>32</v>
-      </c>
-      <c r="G5" t="n">
-        <v>16</v>
-      </c>
-      <c r="H5" t="n">
-        <v>4</v>
+          <t>NPU 필터뱅크 (선형) + CPU 정수 로그</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>ai85safesoundmelnet_p4</t>
+          <t>ai85safesoundfe</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2D CNN, 풀링 4단 (32멜×16프레임 입력)</t>
+          <t>p1 NPU Conv1d 64→64 k=8 (512탭 Gabor 필터뱅크 cos/sin 32쌍, wide int32, 판단당 64위치) → CPU |cos|+|sin|·8위치 합·정수 로그 (32×4 값) → p2 = CPU log-mel 62.5 ms 구성과 같은 2D CNN (1×32×16). 가중치 p1 32 KB + p2 153 KB 동시 적재, 판단 주기 256 ms</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L5" t="n">
-        <v>2393344</v>
+        <v>4261120</v>
       </c>
       <c r="M5" t="n">
-        <v>152.5</v>
+        <v>184.5</v>
       </c>
       <c r="N5" t="n">
-        <v>35.3</v>
+        <v>42.7</v>
       </c>
       <c r="O5" t="n">
-        <v>26337</v>
+        <v>30121</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>data/synth/out/safesound_melu1000_v4d/log.txt·cnn.h; datasets/melfeat.py INC_SPECS</t>
+          <t>data/synth/out/safesound_fe_p1_v4d + data/synth/out/safesound_fe_p2_v4d/log.txt·cnn.h; datasets/melfeat.py INC_SPECS</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CPU log-mel, 간격 50 ms</t>
+          <t>CPU log-mel, 간격 62.5 ms (멜 32)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -688,10 +700,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="D6" t="n">
-        <v>50</v>
+        <v>62.5</v>
       </c>
       <c r="E6" t="n">
         <v>512</v>
@@ -700,10 +712,10 @@
         <v>32</v>
       </c>
       <c r="G6" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -712,14 +724,14 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2D CNN, 풀링 4단 (32멜×20프레임 입력)</t>
+          <t>2D CNN, 풀링 4단 (32멜×16프레임 입력)</t>
         </is>
       </c>
       <c r="K6" t="n">
         <v>7</v>
       </c>
       <c r="L6" t="n">
-        <v>2872576</v>
+        <v>2393344</v>
       </c>
       <c r="M6" t="n">
         <v>152.5</v>
@@ -728,18 +740,18 @@
         <v>35.3</v>
       </c>
       <c r="O6" t="n">
-        <v>32467</v>
+        <v>26337</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>data/synth/out/safesound_melu800_v4d/log.txt·cnn.h; datasets/melfeat.py INC_SPECS</t>
+          <t>data/synth/out/safesound_melu1000_v4d/log.txt·cnn.h; datasets/melfeat.py INC_SPECS</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CPU log-mel, 간격 25 ms</t>
+          <t>CPU log-mel, 간격 50 ms</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -748,38 +760,38 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>400</v>
+        <v>800</v>
       </c>
       <c r="D7" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E7" t="n">
         <v>512</v>
       </c>
       <c r="F7" t="n">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="G7" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="H7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>ai85safesoundmelnet</t>
+          <t>ai85safesoundmelnet_p4</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2D CNN, 풀링 5단 (64멜×40프레임 입력)</t>
+          <t>2D CNN, 풀링 4단 (32멜×20프레임 입력)</t>
         </is>
       </c>
       <c r="K7" t="n">
         <v>7</v>
       </c>
       <c r="L7" t="n">
-        <v>11683072</v>
+        <v>2872576</v>
       </c>
       <c r="M7" t="n">
         <v>152.5</v>
@@ -788,30 +800,30 @@
         <v>35.3</v>
       </c>
       <c r="O7" t="n">
-        <v>127411</v>
+        <v>32467</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>data/synth/out/safesound_melh400_v4d/log.txt·cnn.h; datasets/melfeat.py INC_SPECS</t>
+          <t>data/synth/out/safesound_melu800_v4d/log.txt·cnn.h; datasets/melfeat.py INC_SPECS</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CPU log-mel, 간격 16 ms</t>
+          <t>CPU log-mel, 간격 25 ms</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CPU 로그 멜 (증분, V1 float32 rfft + LUT 로그)</t>
+          <t>CPU 로그 멜 (증분)</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="D8" t="n">
-        <v>15.62</v>
+        <v>25</v>
       </c>
       <c r="E8" t="n">
         <v>512</v>
@@ -820,10 +832,10 @@
         <v>64</v>
       </c>
       <c r="G8" t="n">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="H8" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -832,173 +844,233 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2D CNN, 풀링 5단 (64멜×64프레임 입력)</t>
+          <t>2D CNN, 풀링 5단 (64멜×40프레임 입력)</t>
         </is>
       </c>
       <c r="K8" t="n">
         <v>7</v>
       </c>
       <c r="L8" t="n">
-        <v>18942464</v>
+        <v>11683072</v>
       </c>
       <c r="M8" t="n">
-        <v>153.8</v>
+        <v>152.5</v>
       </c>
       <c r="N8" t="n">
-        <v>35.6</v>
+        <v>35.3</v>
       </c>
       <c r="O8" t="n">
-        <v>204029</v>
+        <v>127411</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>data/synth/out/safesound_melinc_v4d/log.txt·cnn.h; datasets/melfeat.py INC_SPECS</t>
+          <t>data/synth/out/safesound_melh400_v4d/log.txt·cnn.h; datasets/melfeat.py INC_SPECS</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NPU 근사 log</t>
+          <t>CPU log-mel, 간격 16 ms</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>없음 (NPU 안 로그 근사)</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>CPU 로그 멜 (증분, V1 float32 rfft + LUT 로그)</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>250</v>
+      </c>
+      <c r="D9" t="n">
+        <v>15.62</v>
+      </c>
+      <c r="E9" t="n">
+        <v>512</v>
+      </c>
+      <c r="F9" t="n">
+        <v>64</v>
+      </c>
+      <c r="G9" t="n">
+        <v>64</v>
+      </c>
+      <c r="H9" t="n">
+        <v>16</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>ai85safesoundlogstage</t>
+          <t>ai85safesoundmelnet</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>NPU 안에서 구간선형 로그를 근사하는 1D 구성 — 보드 미실측, 지연은 합성 사이클 추정</t>
+          <t>2D CNN, 풀링 5단 (64멜×64프레임 입력)</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="L9" t="n">
-        <v>18581248</v>
+        <v>18942464</v>
       </c>
       <c r="M9" t="n">
-        <v>239.6</v>
+        <v>153.8</v>
       </c>
       <c r="N9" t="n">
-        <v>55.5</v>
+        <v>35.6</v>
       </c>
       <c r="O9" t="n">
-        <v>274726</v>
+        <v>204029</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>data/synth/out/safesound_logstage/log.txt·cnn.h; datasets/melfeat.py INC_SPECS</t>
+          <t>data/synth/out/safesound_melinc_v4d/log.txt·cnn.h; datasets/melfeat.py INC_SPECS</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>NPU 근사 log</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>없음 (NPU 안 로그 근사)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ai85safesoundlogstage</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>NPU 안에서 구간선형 로그를 근사하는 1D 구성 — 보드 미실측, 지연은 합성 사이클 추정</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>11</v>
+      </c>
+      <c r="L10" t="n">
+        <v>18581248</v>
+      </c>
+      <c r="M10" t="n">
+        <v>239.6</v>
+      </c>
+      <c r="N10" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="O10" t="n">
+        <v>274726</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>data/synth/out/safesound_logstage/log.txt·cnn.h; datasets/melfeat.py INC_SPECS</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>CPU 추론 (Cortex-M4F)</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>CMSIS-NN (원본 파형 (전처리 없음) 가중치)</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>④ 와 같은 가중치·같은 출력 (보드 NPU 출력과 비트 일치), arm_convolve_wrapper_s8, -O2</t>
         </is>
       </c>
-      <c r="K10" t="n">
+      <c r="K11" t="n">
         <v>9</v>
       </c>
-      <c r="L10" t="n">
+      <c r="L11" t="n">
         <v>8341248</v>
       </c>
-      <c r="M10" t="n">
+      <c r="M11" t="n">
         <v>161.5</v>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>— (Flash)</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>data/logs-local/board_v4d_m4cmsis.log</t>
         </is>
@@ -1015,7 +1087,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U12"/>
+  <dimension ref="A1:V15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -1039,6 +1111,7 @@
     <col width="40.7" customWidth="1" min="19" max="19"/>
     <col width="20.9" customWidth="1" min="20" max="20"/>
     <col width="20.9" customWidth="1" min="21" max="21"/>
+    <col width="17.6" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1070,326 +1143,135 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>NPU 전처리 (Gabor 필터뱅크) 는 두 네트워크(NPU 필터뱅크 p1 + 2D CNN p2)를 동시 적재한 보드 실측 — CPU 전처리 열 = p1 출력의 |cos|+|sin|·8위치 합·정수 로그 (NPU 전원 켜진 채 → 에너지는 P_load 로), 입력 적재 열 = 두 적재 + 네트워크 전환(층 레지스터 재설정), 추론 열 = p1 + p2. 판단 주기 256 ms (다른 구성 250 ms). 구간별 값은 numbers.json latency.②′.detail.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>파레토 앞면: 점 추정(데이터시트 에너지, 시드 평균) 기준으로 에너지 ≤ 이고 정확도 ≥ 인 다른 구성이 없는 점.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>구성</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>n</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>CPU 전처리 (ms)</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>입력 적재 (ms)</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>추론 (ms)</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>출력 (ms)</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>판단 1회 (ms)</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>판단 주기 대비 (%)</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>지연 출처</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>에너지 (가) 데이터시트 (µJ, 추정)</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>에너지 (나) 선행연구 (Moss / Ulkar &amp; Okman) (µJ, 추정)</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>에너지 (나′) Moss / Moosmann (µJ, 추정)</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>에너지 범위 (µJ, 추정)</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>macro-F1 시험 데이터 (주)</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>macro-F1 시험 데이터 (청취 전 정답, 부록)</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>F1 외부 데이터 (AudioSet)</t>
         </is>
       </c>
-      <c r="Q5" s="2" t="inlineStr">
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>mAP 외부 데이터 (AudioSet)</t>
         </is>
       </c>
-      <c r="R5" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>재현율 시험 데이터 사이렌/유리/비명/개 (%)</t>
         </is>
       </c>
-      <c r="S5" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>재현율 외부 데이터 (AudioSet) 사이렌/유리/비명/개 (%)</t>
         </is>
       </c>
-      <c r="T5" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
         <is>
           <t>외부 배경 264창 발화 (창)</t>
         </is>
       </c>
-      <c r="U5" s="2" t="inlineStr">
+      <c r="U7" s="2" t="inlineStr">
         <is>
           <t>배경+배경 발화율 (%)</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>원본 파형 (전처리 없음)</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>3</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>1.087</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>1.439</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0.008</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>2.53</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>data/logs-local/board_v4d_wave.log</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>71 ~ 130</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0.669 ± 0.025</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>0.647 ± 0.020</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>0.443 ± 0.021</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0.807 ± 0.007</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>56.5 / 55.2 / 28.4 / 61.4</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>31.8 / 31.1 / 3.8 / 31.0</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>1.77</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>CPU log-mel, 간격 62.5 ms (멜 32)</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>3</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>2.264</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>0.134</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0.531</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0.005</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>2.93</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>1.2</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>data/logs-local/board_v4d_u1000.log</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>43 ~ 98</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0.754 ± 0.014</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>0.727 ± 0.011</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0.542 ± 0.014</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>0.844 ± 0.011</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>64.4 / 62.4 / 59.5 / 63.4</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>38.7 / 53.8 / 17.0 / 31.8</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>5.7</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>1.69</t>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>파레토 앞면 (시험 / 외부)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CPU log-mel, 간격 50 ms</t>
+          <t>원본 파형 (전처리 없음)</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -1397,104 +1279,109 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.833</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.167</t>
+          <t>1.087</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.653</t>
+          <t>1.439</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>0.008</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>data/logs-local/board_v4d_u800.log</t>
+          <t>data/logs-local/board_v4d_wave.log</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>71</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>130</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>78</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>54 ~ 121</t>
+          <t>71 ~ 130</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0.758 ± 0.019</t>
+          <t>0.669 ± 0.025</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.733 ± 0.019</t>
+          <t>0.647 ± 0.020</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0.566 ± 0.025</t>
+          <t>0.443 ± 0.021</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>0.866 ± 0.008</t>
+          <t>0.807 ± 0.007</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>63.7 / 67.1 / 56.7 / 65.9</t>
+          <t>56.5 / 55.2 / 28.4 / 61.4</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>44.4 / 56.1 / 15.1 / 38.3</t>
+          <t>31.8 / 31.1 / 3.8 / 31.0</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>— / —</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CPU log-mel, 간격 25 ms</t>
+          <t>NPU 전처리 (Gabor 필터뱅크)</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -1502,17 +1389,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>6.188</t>
+          <t>0.840</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.669</t>
+          <t>0.524</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2.552</t>
+          <t>0.612</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1522,84 +1409,89 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>data/logs-local/board_v4d_h400.log</t>
+          <t>data/logs-local/board_v4d_fe.log</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>353</t>
+          <t>78</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>56</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>167 ~ 353</t>
+          <t>40 ~ 78</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.820 ± 0.006</t>
+          <t>0.643 ± 0.025</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.804 ± 0.006</t>
+          <t>0.619 ± 0.026</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.651 ± 0.010</t>
+          <t>0.460 ± 0.034</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.899 ± 0.003</t>
+          <t>0.794 ± 0.007</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>75.3 / 74.8 / 72.9 / 75.6</t>
+          <t>55.6 / 53.3 / 29.9 / 51.2</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>49.4 / 68.9 / 28.9 / 51.7</t>
+          <t>35.2 / 37.9 / 6.9 / 26.4</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.28</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>○ / ○</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CPU log-mel, 간격 16 ms</t>
+          <t>CPU log-mel, 간격 62.5 ms (멜 32)</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -1607,104 +1499,109 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>9.868</t>
+          <t>2.264</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.096</t>
+          <t>0.134</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>4.086</t>
+          <t>0.531</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>0.005</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>15.06</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>data/logs-local/board_v4d_melinc.log</t>
+          <t>data/logs-local/board_v4d_u1000.log</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>43</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>565</t>
+          <t>98</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>418</t>
+          <t>78</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>267 ~ 565</t>
+          <t>43 ~ 98</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.836 ± 0.002</t>
+          <t>0.754 ± 0.014</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.818 ± 0.003</t>
+          <t>0.727 ± 0.011</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0.665 ± 0.015</t>
+          <t>0.542 ± 0.014</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0.898 ± 0.013</t>
+          <t>0.844 ± 0.011</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>74.6 / 76.7 / 72.4 / 81.6</t>
+          <t>64.4 / 62.4 / 59.5 / 63.4</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>49.4 / 71.2 / 30.2 / 59.4</t>
+          <t>38.7 / 53.8 / 17.0 / 31.8</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>○ / ○</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NPU 근사 log</t>
+          <t>CPU log-mel, 간격 50 ms</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -1712,104 +1609,109 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2.833</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.087</t>
+          <t>0.167</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>5.495 (추정)</t>
+          <t>0.653</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>0.006</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>6.59 (추정)</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>data/synth/out/safesound_logstage/log.txt (Total cycles) ÷ CNN 클럭 50000000 Hz; 적재·출력은 data/logs-local/board_v4d_wave.log (④ 실측)</t>
+          <t>data/logs-local/board_v4d_u800.log</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>54</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>421</t>
+          <t>121</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>98</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>223 ~ 421</t>
+          <t>54 ~ 121</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0.703 ± 0.007</t>
+          <t>0.758 ± 0.019</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>0.678 ± 0.007</t>
+          <t>0.733 ± 0.019</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>0.500 ± 0.011</t>
+          <t>0.566 ± 0.025</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>0.845 ± 0.005</t>
+          <t>0.866 ± 0.008</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>59.0 / 54.3 / 38.6 / 66.9</t>
+          <t>63.7 / 67.1 / 56.7 / 65.9</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>34.1 / 31.8 / 8.2 / 46.7</t>
+          <t>44.4 / 56.1 / 15.1 / 38.3</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.31</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>○ / ○</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CPU 추론 (Cortex-M4F)</t>
+          <t>CPU log-mel, 간격 25 ms</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -1817,97 +1719,432 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>6.188</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>0.669</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2.552</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>0.006</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>9.42</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>3.8</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>data/logs-local/board_v4d_h400.log</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>353</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>167 ~ 353</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>0.820 ± 0.006</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>0.804 ± 0.006</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>0.651 ± 0.010</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>0.899 ± 0.003</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>75.3 / 74.8 / 72.9 / 75.6</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>49.4 / 68.9 / 28.9 / 51.7</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>2.41</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>○ / ○</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CPU log-mel, 간격 16 ms</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>3</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>9.868</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>1.096</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>4.086</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0.008</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>15.06</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>data/logs-local/board_v4d_melinc.log</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>267</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>565</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>418</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>267 ~ 565</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0.836 ± 0.002</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0.818 ± 0.003</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>0.665 ± 0.015</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>0.898 ± 0.013</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>74.6 / 76.7 / 72.4 / 81.6</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>49.4 / 71.2 / 30.2 / 59.4</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>2.39</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>○ / ○</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>NPU 근사 log</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1.087</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>5.495 (추정)</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>0.008</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>6.59 (추정)</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2.6</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>data/synth/out/safesound_logstage/log.txt (Total cycles) ÷ CNN 클럭 50000000 Hz; 적재·출력은 data/logs-local/board_v4d_wave.log (④ 실측)</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>421</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>223 ~ 421</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>0.703 ± 0.007</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>0.678 ± 0.007</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>0.500 ± 0.011</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>0.845 ± 0.005</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>59.0 / 54.3 / 38.6 / 66.9</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>34.1 / 31.8 / 8.2 / 46.7</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>2.16</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>— / —</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CPU 추론 (Cortex-M4F)</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>3</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
         <is>
           <t>0.270</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>225.50</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>225.77</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>90.3</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>data/logs-local/board_v4d_m4cmsis.log</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>2008</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>5599</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>5599</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>2008 ~ 5599</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>원본 파형 (전처리 없음) 와 같다 (같은 가중치·출력)</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>원본 파형 (전처리 없음) 와 같다 (같은 가중치·출력)</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>원본 파형 (전처리 없음) 와 같다 (같은 가중치·출력)</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>원본 파형 (전처리 없음) 와 같다 (같은 가중치·출력)</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="R15" t="inlineStr">
         <is>
           <t>원본 파형 (전처리 없음) 와 같다</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>원본 파형 (전처리 없음) 와 같다</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>원본 파형 (전처리 없음) 와 같다</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>원본 파형 (전처리 없음) 와 같다</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -1922,7 +2159,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -2136,6 +2373,70 @@
       <c r="F8" t="inlineStr">
         <is>
           <t>+0.030 [-0.015, +0.075]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>NPU 전처리 (Gabor 필터뱅크) − 원본 파형 (전처리 없음)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>3 / 3</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>-0.026 [-0.082, +0.030]</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>+0.017 [-0.053, +0.087]</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>-0.014 [-0.029, +0.001]</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>-0.028 [-0.081, +0.026]</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>NPU 전처리 (Gabor 필터뱅크) − CPU log-mel, 간격 62.5 ms (멜 32)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>3 / 3</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>-0.111 [-0.162, -0.060]</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>-0.082 [-0.155, -0.008]</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>-0.050 [-0.074, -0.027]</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>-0.108 [-0.163, -0.053]</t>
         </is>
       </c>
     </row>
@@ -2409,7 +2710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -2423,7 +2724,7 @@
     <col width="57.2" customWidth="1" min="9" max="9"/>
     <col width="45.1" customWidth="1" min="10" max="10"/>
     <col width="40.7" customWidth="1" min="11" max="11"/>
-    <col width="40.7" customWidth="1" min="12" max="12"/>
+    <col width="53.90000000000001" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2809,6 +3110,130 @@
       <c r="L8" t="inlineStr">
         <is>
           <t>NPU 근사 log 지연은 추정 (보드 미실측)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>NPU 전처리 (Gabor 필터뱅크) &lt; 원본 파형 (전처리 없음)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1.371</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>0.612</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1.095</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>1.439</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>r &gt; 0.33</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0.33</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>r = 4.59; E_X 40 / E_Y 71 µJ → 성립</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>r = 2.89; E_X 78 / E_Y 130 µJ → 성립</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>r = 1.44; E_X 56 / E_Y 78 µJ → 성립</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>r = 19.07; E_X 119 / E_Y 256 µJ → 성립</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>선형 전처리를 NPU 로 옮긴 구성이 원본 파형 NPU 보다 적은 조건 (보드 실측)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>NPU 전처리 (Gabor 필터뱅크) &lt; CPU log-mel, 간격 62.5 ms (멜 32)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1.371</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0.612</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2.403</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0.531</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>r &lt; 12.7</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>12.73</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>r = 4.59; E_X 40 / E_Y 43 µJ → 성립</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>r = 2.89; E_X 78 / E_Y 98 µJ → 성립</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>r = 1.44; E_X 56 / E_Y 78 µJ → 성립</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>r = 19.07; E_X 119 / E_Y 112 µJ → 불성립</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>선형 전처리를 NPU 로 옮긴 구성이 CPU log-mel 보다 적은 조건 (보드 실측)</t>
         </is>
       </c>
     </row>

--- a/docs/paper/paper_tables.xlsx
+++ b/docs/paper/paper_tables.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:P14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -691,386 +691,602 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CPU log-mel, 간격 62.5 ms (멜 32)</t>
+          <t>NPU 전처리 64 대역</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CPU 로그 멜 (증분)</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="D6" t="n">
-        <v>62.5</v>
-      </c>
-      <c r="E6" t="n">
-        <v>512</v>
-      </c>
-      <c r="F6" t="n">
-        <v>32</v>
-      </c>
-      <c r="G6" t="n">
-        <v>16</v>
-      </c>
-      <c r="H6" t="n">
-        <v>4</v>
+          <t>NPU 필터뱅크 (선형) + CPU 정수 로그</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>ai85safesoundmelnet_p4</t>
+          <t>ai85safesoundfe_b64</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2D CNN, 풀링 4단 (32멜×16프레임 입력)</t>
+          <t>p1 NPU Conv1d 64→128 k=8 (512탭 Gabor 필터뱅크 cos/sin 64쌍, wide int32, 판단당 64위치) → CPU |cos|+|sin|·8위치 합·정수 로그 (64×4 값) → p2 2D CNN (1×64×16). 두 네트워크 동시 적재, 판단 주기 256 ms</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L6" t="n">
-        <v>2393344</v>
+        <v>8522240</v>
       </c>
       <c r="M6" t="n">
-        <v>152.5</v>
+        <v>217.8</v>
       </c>
       <c r="N6" t="n">
-        <v>35.3</v>
+        <v>50.4</v>
       </c>
       <c r="O6" t="n">
-        <v>26337</v>
+        <v>59859</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>data/synth/out/safesound_melu1000_v4d/log.txt·cnn.h; datasets/melfeat.py INC_SPECS</t>
+          <t>data/synth/out/safesound_fe_b64_p1_v4d + data/synth/out/safesound_fe_b64_p2_v4d/log.txt·cnn.h; datasets/melfeat.py INC_SPECS</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CPU log-mel, 간격 50 ms</t>
+          <t>NPU 전처리 31 프레임</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CPU 로그 멜 (증분)</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>800</v>
-      </c>
-      <c r="D7" t="n">
-        <v>50</v>
-      </c>
-      <c r="E7" t="n">
-        <v>512</v>
-      </c>
-      <c r="F7" t="n">
-        <v>32</v>
-      </c>
-      <c r="G7" t="n">
-        <v>20</v>
-      </c>
-      <c r="H7" t="n">
-        <v>5</v>
+          <t>NPU 필터뱅크 (선형) + CPU 정수 로그</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>ai85safesoundmelnet_p4</t>
+          <t>ai85safesoundfe_f31</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2D CNN, 풀링 4단 (32멜×20프레임 입력)</t>
+          <t>p1 NPU Conv1d 64→64 k=8 (Gabor 32쌍), 입력 71 위치(이전 8 + 새 63) → 출력 64 위치 → CPU 정수 로그 32×8 값/판단 → p2 2D CNN (1×32×31). 두 네트워크 동시 적재, 판단 주기 256 ms</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L7" t="n">
-        <v>2872576</v>
+        <v>6250752</v>
       </c>
       <c r="M7" t="n">
-        <v>152.5</v>
+        <v>184.5</v>
       </c>
       <c r="N7" t="n">
-        <v>35.3</v>
+        <v>42.7</v>
       </c>
       <c r="O7" t="n">
-        <v>32467</v>
+        <v>53135</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>data/synth/out/safesound_melu800_v4d/log.txt·cnn.h; datasets/melfeat.py INC_SPECS</t>
+          <t>data/synth/out/safesound_fe_f31_p1_v4d + data/synth/out/safesound_fe_f31_p2_v4d/log.txt·cnn.h; datasets/melfeat.py INC_SPECS</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CPU log-mel, 간격 25 ms</t>
+          <t>NPU 전처리 64 대역·31 프레임</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CPU 로그 멜 (증분)</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>400</v>
-      </c>
-      <c r="D8" t="n">
-        <v>25</v>
-      </c>
-      <c r="E8" t="n">
-        <v>512</v>
-      </c>
-      <c r="F8" t="n">
-        <v>64</v>
-      </c>
-      <c r="G8" t="n">
-        <v>40</v>
-      </c>
-      <c r="H8" t="n">
-        <v>10</v>
+          <t>NPU 필터뱅크 (선형) + CPU 정수 로그</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ai85safesoundmelnet</t>
+          <t>ai85safesoundfe_b64f31</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2D CNN, 풀링 5단 (64멜×40프레임 입력)</t>
+          <t>p1 NPU Conv1d 64→128 k=8 (Gabor 64쌍), 입력 71 위치 → CPU 정수 로그 64×8 값/판단 → p2 2D CNN (1×64×31). 두 네트워크 동시 적재, 판단 주기 256 ms</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L8" t="n">
-        <v>11683072</v>
+        <v>12501504</v>
       </c>
       <c r="M8" t="n">
-        <v>152.5</v>
+        <v>217.8</v>
       </c>
       <c r="N8" t="n">
-        <v>35.3</v>
+        <v>50.4</v>
       </c>
       <c r="O8" t="n">
-        <v>127411</v>
+        <v>105717</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>data/synth/out/safesound_melh400_v4d/log.txt·cnn.h; datasets/melfeat.py INC_SPECS</t>
+          <t>data/synth/out/safesound_fe_b64f31_p1_v4d + data/synth/out/safesound_fe_b64f31_p2_v4d/log.txt·cnn.h; datasets/melfeat.py INC_SPECS</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CPU log-mel, 간격 16 ms</t>
+          <t>CPU log-mel, 간격 62.5 ms (멜 32)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CPU 로그 멜 (증분, V1 float32 rfft + LUT 로그)</t>
+          <t>CPU 로그 멜 (증분)</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="D9" t="n">
-        <v>15.62</v>
+        <v>62.5</v>
       </c>
       <c r="E9" t="n">
         <v>512</v>
       </c>
       <c r="F9" t="n">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="G9" t="n">
-        <v>64</v>
+        <v>16</v>
       </c>
       <c r="H9" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>ai85safesoundmelnet</t>
+          <t>ai85safesoundmelnet_p4</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2D CNN, 풀링 5단 (64멜×64프레임 입력)</t>
+          <t>2D CNN, 풀링 4단 (32멜×16프레임 입력)</t>
         </is>
       </c>
       <c r="K9" t="n">
         <v>7</v>
       </c>
       <c r="L9" t="n">
-        <v>18942464</v>
+        <v>2393344</v>
       </c>
       <c r="M9" t="n">
-        <v>153.8</v>
+        <v>152.5</v>
       </c>
       <c r="N9" t="n">
-        <v>35.6</v>
+        <v>35.3</v>
       </c>
       <c r="O9" t="n">
-        <v>204029</v>
+        <v>26337</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>data/synth/out/safesound_melinc_v4d/log.txt·cnn.h; datasets/melfeat.py INC_SPECS</t>
+          <t>data/synth/out/safesound_melu1000_v4d/log.txt·cnn.h; datasets/melfeat.py INC_SPECS</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NPU 근사 log</t>
+          <t>CPU log-mel, 간격 50 ms</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>없음 (NPU 안 로그 근사)</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>CPU 로그 멜 (증분)</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>800</v>
+      </c>
+      <c r="D10" t="n">
+        <v>50</v>
+      </c>
+      <c r="E10" t="n">
+        <v>512</v>
+      </c>
+      <c r="F10" t="n">
+        <v>32</v>
+      </c>
+      <c r="G10" t="n">
+        <v>20</v>
+      </c>
+      <c r="H10" t="n">
+        <v>5</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>ai85safesoundlogstage</t>
+          <t>ai85safesoundmelnet_p4</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>NPU 안에서 구간선형 로그를 근사하는 1D 구성 — 보드 미실측, 지연은 합성 사이클 추정</t>
+          <t>2D CNN, 풀링 4단 (32멜×20프레임 입력)</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="L10" t="n">
-        <v>18581248</v>
+        <v>2872576</v>
       </c>
       <c r="M10" t="n">
-        <v>239.6</v>
+        <v>152.5</v>
       </c>
       <c r="N10" t="n">
-        <v>55.5</v>
+        <v>35.3</v>
       </c>
       <c r="O10" t="n">
-        <v>274726</v>
+        <v>32467</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>data/synth/out/safesound_logstage/log.txt·cnn.h; datasets/melfeat.py INC_SPECS</t>
+          <t>data/synth/out/safesound_melu800_v4d/log.txt·cnn.h; datasets/melfeat.py INC_SPECS</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>CPU log-mel, 간격 25 ms</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>CPU 로그 멜 (증분)</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>400</v>
+      </c>
+      <c r="D11" t="n">
+        <v>25</v>
+      </c>
+      <c r="E11" t="n">
+        <v>512</v>
+      </c>
+      <c r="F11" t="n">
+        <v>64</v>
+      </c>
+      <c r="G11" t="n">
+        <v>40</v>
+      </c>
+      <c r="H11" t="n">
+        <v>10</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ai85safesoundmelnet</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>2D CNN, 풀링 5단 (64멜×40프레임 입력)</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>7</v>
+      </c>
+      <c r="L11" t="n">
+        <v>11683072</v>
+      </c>
+      <c r="M11" t="n">
+        <v>152.5</v>
+      </c>
+      <c r="N11" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="O11" t="n">
+        <v>127411</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>data/synth/out/safesound_melh400_v4d/log.txt·cnn.h; datasets/melfeat.py INC_SPECS</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CPU log-mel, 간격 16 ms</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>CPU 로그 멜 (증분, V1 float32 rfft + LUT 로그)</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>250</v>
+      </c>
+      <c r="D12" t="n">
+        <v>15.62</v>
+      </c>
+      <c r="E12" t="n">
+        <v>512</v>
+      </c>
+      <c r="F12" t="n">
+        <v>64</v>
+      </c>
+      <c r="G12" t="n">
+        <v>64</v>
+      </c>
+      <c r="H12" t="n">
+        <v>16</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ai85safesoundmelnet</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>2D CNN, 풀링 5단 (64멜×64프레임 입력)</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>7</v>
+      </c>
+      <c r="L12" t="n">
+        <v>18942464</v>
+      </c>
+      <c r="M12" t="n">
+        <v>153.8</v>
+      </c>
+      <c r="N12" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="O12" t="n">
+        <v>204029</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>data/synth/out/safesound_melinc_v4d/log.txt·cnn.h; datasets/melfeat.py INC_SPECS</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>NPU 근사 log</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>없음 (NPU 안 로그 근사)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ai85safesoundlogstage</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>NPU 안에서 구간선형 로그를 근사하는 1D 구성 — 보드 미실측, 지연은 합성 사이클 추정</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>11</v>
+      </c>
+      <c r="L13" t="n">
+        <v>18581248</v>
+      </c>
+      <c r="M13" t="n">
+        <v>239.6</v>
+      </c>
+      <c r="N13" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="O13" t="n">
+        <v>274726</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>data/synth/out/safesound_logstage/log.txt·cnn.h; datasets/melfeat.py INC_SPECS</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>CPU 추론 (Cortex-M4F)</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
         <is>
           <t>CMSIS-NN (원본 파형 (전처리 없음) 가중치)</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>④ 와 같은 가중치·같은 출력 (보드 NPU 출력과 비트 일치), arm_convolve_wrapper_s8, -O2</t>
         </is>
       </c>
-      <c r="K11" t="n">
+      <c r="K14" t="n">
         <v>9</v>
       </c>
-      <c r="L11" t="n">
+      <c r="L14" t="n">
         <v>8341248</v>
       </c>
-      <c r="M11" t="n">
+      <c r="M14" t="n">
         <v>161.5</v>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>— (Flash)</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
         <is>
           <t>data/logs-local/board_v4d_m4cmsis.log</t>
         </is>
@@ -1087,7 +1303,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V15"/>
+  <dimension ref="A1:V19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -1152,236 +1368,133 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
+          <t>NPU 전처리 64 대역 / NPU 전처리 31 프레임 / NPU 전처리 64 대역·31 프레임 은 NPU 전처리 (Gabor 필터뱅크) 의 대역·프레임 수를 늘린 변형 (사전 등록 docs/results/fe-curve-design.md) — 같은 두 네트워크 보드 실측, 같은 열 정의. 예측·하한과의 비교는 numbers.json variants.②′.measured.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
           <t>파레토 앞면: 점 추정(데이터시트 에너지, 시드 평균) 기준으로 에너지 ≤ 이고 정확도 ≥ 인 다른 구성이 없는 점.</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>구성</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>n</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>CPU 전처리 (ms)</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>입력 적재 (ms)</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>추론 (ms)</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>출력 (ms)</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>판단 1회 (ms)</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>판단 주기 대비 (%)</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>지연 출처</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>에너지 (가) 데이터시트 (µJ, 추정)</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>에너지 (나) 선행연구 (Moss / Ulkar &amp; Okman) (µJ, 추정)</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>에너지 (나′) Moss / Moosmann (µJ, 추정)</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>에너지 범위 (µJ, 추정)</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>macro-F1 시험 데이터 (주)</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>macro-F1 시험 데이터 (청취 전 정답, 부록)</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>F1 외부 데이터 (AudioSet)</t>
         </is>
       </c>
-      <c r="Q7" s="2" t="inlineStr">
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>mAP 외부 데이터 (AudioSet)</t>
         </is>
       </c>
-      <c r="R7" s="2" t="inlineStr">
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>재현율 시험 데이터 사이렌/유리/비명/개 (%)</t>
         </is>
       </c>
-      <c r="S7" s="2" t="inlineStr">
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>재현율 외부 데이터 (AudioSet) 사이렌/유리/비명/개 (%)</t>
         </is>
       </c>
-      <c r="T7" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
         <is>
           <t>외부 배경 264창 발화 (창)</t>
         </is>
       </c>
-      <c r="U7" s="2" t="inlineStr">
+      <c r="U8" s="2" t="inlineStr">
         <is>
           <t>배경+배경 발화율 (%)</t>
         </is>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>파레토 앞면 (시험 / 외부)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>원본 파형 (전처리 없음)</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>3</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>1.087</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>1.439</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0.008</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>2.53</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>data/logs-local/board_v4d_wave.log</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>71 ~ 130</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0.669 ± 0.025</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0.647 ± 0.020</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>0.443 ± 0.021</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>0.807 ± 0.007</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>56.5 / 55.2 / 28.4 / 61.4</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>31.8 / 31.1 / 3.8 / 31.0</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>1.77</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>— / —</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NPU 전처리 (Gabor 필터뱅크)</t>
+          <t>원본 파형 (전처리 없음)</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -1389,109 +1502,109 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.840</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.524</t>
+          <t>1.087</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.612</t>
+          <t>1.439</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>0.008</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>data/logs-local/board_v4d_fe.log</t>
+          <t>data/logs-local/board_v4d_wave.log</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>71</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
           <t>78</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>40 ~ 78</t>
+          <t>71 ~ 130</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.643 ± 0.025</t>
+          <t>0.669 ± 0.025</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.619 ± 0.026</t>
+          <t>0.647 ± 0.020</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.460 ± 0.034</t>
+          <t>0.443 ± 0.021</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.794 ± 0.007</t>
+          <t>0.807 ± 0.007</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>55.6 / 53.3 / 29.9 / 51.2</t>
+          <t>56.5 / 55.2 / 28.4 / 61.4</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>35.2 / 37.9 / 6.9 / 26.4</t>
+          <t>31.8 / 31.1 / 3.8 / 31.0</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>○ / ○</t>
+          <t>— / —</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CPU log-mel, 간격 62.5 ms (멜 32)</t>
+          <t>NPU 전처리 (Gabor 필터뱅크)</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -1499,97 +1612,97 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.264</t>
+          <t>0.840</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.134</t>
+          <t>0.524</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.531</t>
+          <t>0.612</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>0.006</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>data/logs-local/board_v4d_u1000.log</t>
+          <t>data/logs-local/board_v4d_fe.log</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>78</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>56</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>43 ~ 98</t>
+          <t>40 ~ 78</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.754 ± 0.014</t>
+          <t>0.643 ± 0.025</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.727 ± 0.011</t>
+          <t>0.619 ± 0.026</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0.542 ± 0.014</t>
+          <t>0.460 ± 0.034</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0.844 ± 0.011</t>
+          <t>0.794 ± 0.007</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>64.4 / 62.4 / 59.5 / 63.4</t>
+          <t>55.6 / 53.3 / 29.9 / 51.2</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>38.7 / 53.8 / 17.0 / 31.8</t>
+          <t>35.2 / 37.9 / 6.9 / 26.4</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1601,7 +1714,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CPU log-mel, 간격 50 ms</t>
+          <t>NPU 전처리 64 대역</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -1609,22 +1722,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2.833</t>
+          <t>1.678</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.167</t>
+          <t>0.665</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.653</t>
+          <t>1.305</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>0.008</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1639,79 +1752,79 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>data/logs-local/board_v4d_u800.log</t>
+          <t>data/logs-local/board_v4d_fe_b64.log</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>80</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>152</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>105</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>54 ~ 121</t>
+          <t>80 ~ 152</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0.758 ± 0.019</t>
+          <t>0.687 ± 0.005</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>0.733 ± 0.019</t>
+          <t>0.663 ± 0.012</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>0.566 ± 0.025</t>
+          <t>0.504 ± 0.021</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>0.866 ± 0.008</t>
+          <t>0.822 ± 0.003</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>63.7 / 67.1 / 56.7 / 65.9</t>
+          <t>60.1 / 52.9 / 38.8 / 57.6</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>44.4 / 56.1 / 15.1 / 38.3</t>
+          <t>36.4 / 52.3 / 6.9 / 31.0</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>○ / ○</t>
+          <t>— / —</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CPU log-mel, 간격 25 ms</t>
+          <t>NPU 전처리 31 프레임</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -1719,109 +1832,109 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>6.188</t>
+          <t>1.661</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.669</t>
+          <t>0.683</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2.552</t>
+          <t>1.171</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>0.008</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>data/logs-local/board_v4d_h400.log</t>
+          <t>data/logs-local/board_v4d_fe_f31.log</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>74</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>353</t>
+          <t>142</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>100</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>167 ~ 353</t>
+          <t>74 ~ 142</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>0.820 ± 0.006</t>
+          <t>0.655 ± 0.011</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>0.804 ± 0.006</t>
+          <t>0.634 ± 0.012</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>0.651 ± 0.010</t>
+          <t>0.465 ± 0.006</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>0.899 ± 0.003</t>
+          <t>0.818 ± 0.012</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>75.3 / 74.8 / 72.9 / 75.6</t>
+          <t>54.4 / 57.6 / 29.9 / 53.4</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>49.4 / 68.9 / 28.9 / 51.7</t>
+          <t>29.9 / 43.9 / 5.0 / 31.0</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>○ / ○</t>
+          <t>— / —</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CPU log-mel, 간격 16 ms</t>
+          <t>NPU 전처리 64 대역·31 프레임</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1829,109 +1942,109 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>9.868</t>
+          <t>3.319</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.096</t>
+          <t>0.946</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>4.086</t>
+          <t>2.222</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>0.007</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>15.06</t>
+          <t>6.49</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
+          <t>2.6</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>data/logs-local/board_v4d_fe_b64f31.log</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>139 ~ 265</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0.690 ± 0.021</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0.673 ± 0.022</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>0.508 ± 0.023</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>0.826 ± 0.020</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>60.8 / 61.0 / 32.8 / 60.4</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>36.4 / 50.0 / 9.4 / 32.2</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
           <t>6.0</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>data/logs-local/board_v4d_melinc.log</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>267</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>565</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>418</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>267 ~ 565</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>0.836 ± 0.002</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>0.818 ± 0.003</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>0.665 ± 0.015</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>0.898 ± 0.013</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>74.6 / 76.7 / 72.4 / 81.6</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>49.4 / 71.2 / 30.2 / 59.4</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>4.3</t>
-        </is>
-      </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>○ / ○</t>
+          <t>— / —</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>NPU 근사 log</t>
+          <t>CPU log-mel, 간격 62.5 ms (멜 32)</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -1939,109 +2052,109 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2.264</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.087</t>
+          <t>0.134</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>5.495 (추정)</t>
+          <t>0.531</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>0.005</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>6.59 (추정)</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>data/synth/out/safesound_logstage/log.txt (Total cycles) ÷ CNN 클럭 50000000 Hz; 적재·출력은 data/logs-local/board_v4d_wave.log (④ 실측)</t>
+          <t>data/logs-local/board_v4d_u1000.log</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>43</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>421</t>
+          <t>98</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>78</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>223 ~ 421</t>
+          <t>43 ~ 98</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>0.703 ± 0.007</t>
+          <t>0.754 ± 0.014</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>0.678 ± 0.007</t>
+          <t>0.727 ± 0.011</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>0.500 ± 0.011</t>
+          <t>0.542 ± 0.014</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>0.845 ± 0.005</t>
+          <t>0.844 ± 0.011</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>59.0 / 54.3 / 38.6 / 66.9</t>
+          <t>64.4 / 62.4 / 59.5 / 63.4</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>34.1 / 31.8 / 8.2 / 46.7</t>
+          <t>38.7 / 53.8 / 17.0 / 31.8</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>— / —</t>
+          <t>○ / ○</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CPU 추론 (Cortex-M4F)</t>
+          <t>CPU log-mel, 간격 50 ms</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -2049,100 +2162,540 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2.833</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>0.167</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0.653</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>0.006</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>3.66</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>data/logs-local/board_v4d_u800.log</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>54 ~ 121</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>0.758 ± 0.019</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>0.733 ± 0.019</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>0.566 ± 0.025</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>0.866 ± 0.008</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>63.7 / 67.1 / 56.7 / 65.9</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>44.4 / 56.1 / 15.1 / 38.3</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>2.31</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>○ / ○</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>CPU log-mel, 간격 25 ms</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>6.188</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>0.669</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2.552</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>0.006</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>9.42</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>3.8</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>data/logs-local/board_v4d_h400.log</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>353</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>167 ~ 353</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>0.820 ± 0.006</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>0.804 ± 0.006</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>0.651 ± 0.010</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>0.899 ± 0.003</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>75.3 / 74.8 / 72.9 / 75.6</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>49.4 / 68.9 / 28.9 / 51.7</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>2.41</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>○ / ○</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>CPU log-mel, 간격 16 ms</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>3</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>9.868</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>1.096</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>4.086</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>0.008</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>15.06</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>data/logs-local/board_v4d_melinc.log</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>267</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>565</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>418</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>267 ~ 565</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>0.836 ± 0.002</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>0.818 ± 0.003</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>0.665 ± 0.015</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>0.898 ± 0.013</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>74.6 / 76.7 / 72.4 / 81.6</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>49.4 / 71.2 / 30.2 / 59.4</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>2.39</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>○ / ○</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>NPU 근사 log</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>3</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>1.087</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>5.495 (추정)</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>0.008</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>6.59 (추정)</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2.6</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>data/synth/out/safesound_logstage/log.txt (Total cycles) ÷ CNN 클럭 50000000 Hz; 적재·출력은 data/logs-local/board_v4d_wave.log (④ 실측)</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>421</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>223 ~ 421</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>0.703 ± 0.007</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0.678 ± 0.007</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>0.500 ± 0.011</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>0.845 ± 0.005</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>59.0 / 54.3 / 38.6 / 66.9</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>34.1 / 31.8 / 8.2 / 46.7</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>2.16</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>— / —</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>CPU 추론 (Cortex-M4F)</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>3</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
           <t>0.270</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>225.50</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
         <is>
           <t>225.77</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>90.3</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>data/logs-local/board_v4d_m4cmsis.log</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>2008</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>5599</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>5599</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>2008 ~ 5599</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>원본 파형 (전처리 없음) 와 같다 (같은 가중치·출력)</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>원본 파형 (전처리 없음) 와 같다 (같은 가중치·출력)</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>원본 파형 (전처리 없음) 와 같다 (같은 가중치·출력)</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="Q19" t="inlineStr">
         <is>
           <t>원본 파형 (전처리 없음) 와 같다 (같은 가중치·출력)</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="R19" t="inlineStr">
         <is>
           <t>원본 파형 (전처리 없음) 와 같다</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>원본 파형 (전처리 없음) 와 같다</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>원본 파형 (전처리 없음) 와 같다</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>원본 파형 (전처리 없음) 와 같다</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/docs/paper/paper_tables.xlsx
+++ b/docs/paper/paper_tables.xlsx
@@ -1303,7 +1303,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V19"/>
+  <dimension ref="A1:V21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -1375,346 +1375,136 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
+          <t>변형 3종은 펌웨어 안정화 대기(NPU 패스당 약 49 µs) 포함 — 에너지 최대 약 7 µJ 과대(측정값에서 빼지 않음). 같은 대기를 넣으면 NPU 전처리 (Gabor 필터뱅크) 는 2.09 ms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
           <t>파레토 앞면: 점 추정(데이터시트 에너지, 시드 평균) 기준으로 에너지 ≤ 이고 정확도 ≥ 인 다른 구성이 없는 점.</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>구성</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>n</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>CPU 전처리 (ms)</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>입력 적재 (ms)</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>추론 (ms)</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>출력 (ms)</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>판단 1회 (ms)</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>판단 주기 대비 (%)</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>지연 출처</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>에너지 (가) 데이터시트 (µJ, 추정)</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>에너지 (나) 선행연구 (Moss / Ulkar &amp; Okman) (µJ, 추정)</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>에너지 (나′) Moss / Moosmann (µJ, 추정)</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>에너지 범위 (µJ, 추정)</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>macro-F1 시험 데이터 (주)</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>macro-F1 시험 데이터 (청취 전 정답, 부록)</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>F1 외부 데이터 (AudioSet)</t>
         </is>
       </c>
-      <c r="Q8" s="2" t="inlineStr">
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>mAP 외부 데이터 (AudioSet)</t>
         </is>
       </c>
-      <c r="R8" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>재현율 시험 데이터 사이렌/유리/비명/개 (%)</t>
         </is>
       </c>
-      <c r="S8" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>재현율 외부 데이터 (AudioSet) 사이렌/유리/비명/개 (%)</t>
         </is>
       </c>
-      <c r="T8" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
         <is>
           <t>외부 배경 264창 발화 (창)</t>
         </is>
       </c>
-      <c r="U8" s="2" t="inlineStr">
+      <c r="U10" s="2" t="inlineStr">
         <is>
           <t>배경+배경 발화율 (%)</t>
         </is>
       </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>파레토 앞면 (시험 / 외부)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>원본 파형 (전처리 없음)</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>3</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>1.087</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>1.439</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>0.008</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>2.53</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>data/logs-local/board_v4d_wave.log</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>71 ~ 130</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0.669 ± 0.025</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>0.647 ± 0.020</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0.443 ± 0.021</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0.807 ± 0.007</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>56.5 / 55.2 / 28.4 / 61.4</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>31.8 / 31.1 / 3.8 / 31.0</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>1.77</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>— / —</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>NPU 전처리 (Gabor 필터뱅크)</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>3</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>0.840</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>0.524</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0.612</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>0.006</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>1.98</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0.8</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>data/logs-local/board_v4d_fe.log</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>40 ~ 78</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0.643 ± 0.025</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>0.619 ± 0.026</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0.460 ± 0.034</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0.794 ± 0.007</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>55.6 / 53.3 / 29.9 / 51.2</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>35.2 / 37.9 / 6.9 / 26.4</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>2.28</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>○ / ○</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NPU 전처리 64 대역</t>
+          <t>원본 파형 (전처리 없음)</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -1722,17 +1512,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.678</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.665</t>
+          <t>1.087</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.305</t>
+          <t>1.439</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1742,77 +1532,77 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>data/logs-local/board_v4d_fe_b64.log</t>
+          <t>data/logs-local/board_v4d_wave.log</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>71</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>130</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>78</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>80 ~ 152</t>
+          <t>71 ~ 130</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0.687 ± 0.005</t>
+          <t>0.669 ± 0.025</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>0.663 ± 0.012</t>
+          <t>0.647 ± 0.020</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>0.504 ± 0.021</t>
+          <t>0.443 ± 0.021</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>0.822 ± 0.003</t>
+          <t>0.807 ± 0.007</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>60.1 / 52.9 / 38.8 / 57.6</t>
+          <t>56.5 / 55.2 / 28.4 / 61.4</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>36.4 / 52.3 / 6.9 / 31.0</t>
+          <t>31.8 / 31.1 / 3.8 / 31.0</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1824,7 +1614,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NPU 전처리 31 프레임</t>
+          <t>NPU 전처리 (Gabor 필터뱅크)</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -1832,109 +1622,109 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.661</t>
+          <t>0.840</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.683</t>
+          <t>0.524</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.171</t>
+          <t>0.612</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>0.006</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>data/logs-local/board_v4d_fe_f31.log</t>
+          <t>data/logs-local/board_v4d_fe_oldfw.log</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>78</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>56</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>74 ~ 142</t>
+          <t>40 ~ 78</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>0.655 ± 0.011</t>
+          <t>0.643 ± 0.025</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>0.634 ± 0.012</t>
+          <t>0.619 ± 0.026</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>0.465 ± 0.006</t>
+          <t>0.460 ± 0.034</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>0.818 ± 0.012</t>
+          <t>0.794 ± 0.007</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>54.4 / 57.6 / 29.9 / 53.4</t>
+          <t>55.6 / 53.3 / 29.9 / 51.2</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>29.9 / 43.9 / 5.0 / 31.0</t>
+          <t>35.2 / 37.9 / 6.9 / 26.4</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>— / —</t>
+          <t>○ / ○</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NPU 전처리 64 대역·31 프레임</t>
+          <t>NPU 전처리 64 대역</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1942,97 +1732,97 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>3.319</t>
+          <t>1.678</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.946</t>
+          <t>0.665</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2.222</t>
+          <t>1.305</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>0.008</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>6.49</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>data/logs-local/board_v4d_fe_b64f31.log</t>
+          <t>data/logs-local/board_v4d_fe_b64.log</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>80</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>152</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>105</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>139 ~ 265</t>
+          <t>80 ~ 152</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>0.690 ± 0.021</t>
+          <t>0.687 ± 0.005</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>0.673 ± 0.022</t>
+          <t>0.663 ± 0.012</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>0.508 ± 0.023</t>
+          <t>0.504 ± 0.021</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>0.826 ± 0.020</t>
+          <t>0.822 ± 0.003</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>60.8 / 61.0 / 32.8 / 60.4</t>
+          <t>60.1 / 52.9 / 38.8 / 57.6</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>36.4 / 50.0 / 9.4 / 32.2</t>
+          <t>36.4 / 52.3 / 6.9 / 31.0</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -2044,7 +1834,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CPU log-mel, 간격 62.5 ms (멜 32)</t>
+          <t>NPU 전처리 31 프레임</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -2052,109 +1842,109 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2.264</t>
+          <t>1.661</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.134</t>
+          <t>0.683</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.531</t>
+          <t>1.171</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>0.008</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>data/logs-local/board_v4d_u1000.log</t>
+          <t>data/logs-local/board_v4d_fe_f31.log</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>74</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>142</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>100</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>43 ~ 98</t>
+          <t>74 ~ 142</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>0.754 ± 0.014</t>
+          <t>0.655 ± 0.011</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>0.727 ± 0.011</t>
+          <t>0.634 ± 0.012</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>0.542 ± 0.014</t>
+          <t>0.465 ± 0.006</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>0.844 ± 0.011</t>
+          <t>0.818 ± 0.012</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>64.4 / 62.4 / 59.5 / 63.4</t>
+          <t>54.4 / 57.6 / 29.9 / 53.4</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>38.7 / 53.8 / 17.0 / 31.8</t>
+          <t>29.9 / 43.9 / 5.0 / 31.0</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>○ / ○</t>
+          <t>— / —</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CPU log-mel, 간격 50 ms</t>
+          <t>NPU 전처리 64 대역·31 프레임</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -2162,109 +1952,109 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2.833</t>
+          <t>3.319</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.167</t>
+          <t>0.946</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.653</t>
+          <t>2.222</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>0.007</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>6.49</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>data/logs-local/board_v4d_u800.log</t>
+          <t>data/logs-local/board_v4d_fe_b64f31.log</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>139</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>265</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>185</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>54 ~ 121</t>
+          <t>139 ~ 265</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>0.758 ± 0.019</t>
+          <t>0.690 ± 0.021</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>0.733 ± 0.019</t>
+          <t>0.673 ± 0.022</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>0.566 ± 0.025</t>
+          <t>0.508 ± 0.023</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>0.866 ± 0.008</t>
+          <t>0.826 ± 0.020</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>63.7 / 67.1 / 56.7 / 65.9</t>
+          <t>60.8 / 61.0 / 32.8 / 60.4</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>44.4 / 56.1 / 15.1 / 38.3</t>
+          <t>36.4 / 50.0 / 9.4 / 32.2</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>○ / ○</t>
+          <t>— / —</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CPU log-mel, 간격 25 ms</t>
+          <t>CPU log-mel, 간격 62.5 ms (멜 32)</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -2272,97 +2062,97 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>6.188</t>
+          <t>2.264</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.669</t>
+          <t>0.134</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2.552</t>
+          <t>0.531</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>0.005</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>data/logs-local/board_v4d_h400.log</t>
+          <t>data/logs-local/board_v4d_u1000.log</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>43</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>353</t>
+          <t>98</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>78</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>167 ~ 353</t>
+          <t>43 ~ 98</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>0.820 ± 0.006</t>
+          <t>0.754 ± 0.014</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>0.804 ± 0.006</t>
+          <t>0.727 ± 0.011</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>0.651 ± 0.010</t>
+          <t>0.542 ± 0.014</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>0.899 ± 0.003</t>
+          <t>0.844 ± 0.011</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>75.3 / 74.8 / 72.9 / 75.6</t>
+          <t>64.4 / 62.4 / 59.5 / 63.4</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>49.4 / 68.9 / 28.9 / 51.7</t>
+          <t>38.7 / 53.8 / 17.0 / 31.8</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -2374,7 +2164,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CPU log-mel, 간격 16 ms</t>
+          <t>CPU log-mel, 간격 50 ms</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -2382,97 +2172,97 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>9.868</t>
+          <t>2.833</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.096</t>
+          <t>0.167</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>4.086</t>
+          <t>0.653</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>0.006</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>15.06</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>data/logs-local/board_v4d_melinc.log</t>
+          <t>data/logs-local/board_v4d_u800.log</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>54</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>565</t>
+          <t>121</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>418</t>
+          <t>98</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>267 ~ 565</t>
+          <t>54 ~ 121</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>0.836 ± 0.002</t>
+          <t>0.758 ± 0.019</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>0.818 ± 0.003</t>
+          <t>0.733 ± 0.019</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>0.665 ± 0.015</t>
+          <t>0.566 ± 0.025</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>0.898 ± 0.013</t>
+          <t>0.866 ± 0.008</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>74.6 / 76.7 / 72.4 / 81.6</t>
+          <t>63.7 / 67.1 / 56.7 / 65.9</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>49.4 / 71.2 / 30.2 / 59.4</t>
+          <t>44.4 / 56.1 / 15.1 / 38.3</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -2484,7 +2274,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>NPU 근사 log</t>
+          <t>CPU log-mel, 간격 25 ms</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -2492,109 +2282,109 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.188</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.087</t>
+          <t>0.669</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>5.495 (추정)</t>
+          <t>2.552</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>0.006</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>6.59 (추정)</t>
+          <t>9.42</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>data/synth/out/safesound_logstage/log.txt (Total cycles) ÷ CNN 클럭 50000000 Hz; 적재·출력은 data/logs-local/board_v4d_wave.log (④ 실측)</t>
+          <t>data/logs-local/board_v4d_h400.log</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>167</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>421</t>
+          <t>353</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>261</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>223 ~ 421</t>
+          <t>167 ~ 353</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>0.703 ± 0.007</t>
+          <t>0.820 ± 0.006</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>0.678 ± 0.007</t>
+          <t>0.804 ± 0.006</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>0.500 ± 0.011</t>
+          <t>0.651 ± 0.010</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>0.845 ± 0.005</t>
+          <t>0.899 ± 0.003</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>59.0 / 54.3 / 38.6 / 66.9</t>
+          <t>75.3 / 74.8 / 72.9 / 75.6</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>34.1 / 31.8 / 8.2 / 46.7</t>
+          <t>49.4 / 68.9 / 28.9 / 51.7</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>— / —</t>
+          <t>○ / ○</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CPU 추론 (Cortex-M4F)</t>
+          <t>CPU log-mel, 간격 16 ms</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -2602,100 +2392,320 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9.868</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>1.096</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>4.086</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0.008</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>15.06</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>data/logs-local/board_v4d_melinc.log</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>267</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>565</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>418</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>267 ~ 565</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0.836 ± 0.002</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0.818 ± 0.003</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>0.665 ± 0.015</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>0.898 ± 0.013</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>74.6 / 76.7 / 72.4 / 81.6</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>49.4 / 71.2 / 30.2 / 59.4</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>2.39</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>○ / ○</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>NPU 근사 log</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>3</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1.087</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>5.495 (추정)</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>0.008</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>6.59 (추정)</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2.6</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>data/synth/out/safesound_logstage/log.txt (Total cycles) ÷ CNN 클럭 50000000 Hz; 적재·출력은 data/logs-local/board_v4d_wave.log (④ 실측)</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>421</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>223 ~ 421</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>0.703 ± 0.007</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>0.678 ± 0.007</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>0.500 ± 0.011</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>0.845 ± 0.005</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>59.0 / 54.3 / 38.6 / 66.9</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>34.1 / 31.8 / 8.2 / 46.7</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>2.16</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>— / —</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>CPU 추론 (Cortex-M4F)</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>3</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
           <t>0.270</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>225.50</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
         <is>
           <t>225.77</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>90.3</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>data/logs-local/board_v4d_m4cmsis.log</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>2008</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>5599</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>5599</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>2008 ~ 5599</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>원본 파형 (전처리 없음) 와 같다 (같은 가중치·출력)</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>원본 파형 (전처리 없음) 와 같다 (같은 가중치·출력)</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>원본 파형 (전처리 없음) 와 같다 (같은 가중치·출력)</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>원본 파형 (전처리 없음) 와 같다 (같은 가중치·출력)</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="R21" t="inlineStr">
         <is>
           <t>원본 파형 (전처리 없음) 와 같다</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>원본 파형 (전처리 없음) 와 같다</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>원본 파형 (전처리 없음) 와 같다</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>원본 파형 (전처리 없음) 와 같다</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/docs/paper/paper_tables.xlsx
+++ b/docs/paper/paper_tables.xlsx
@@ -1375,7 +1375,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>변형 3종은 펌웨어 안정화 대기(NPU 패스당 약 49 µs) 포함 — 에너지 최대 약 7 µJ 과대(측정값에서 빼지 않음). 같은 대기를 넣으면 NPU 전처리 (Gabor 필터뱅크) 는 2.09 ms.</t>
+          <t>변형 3종은 펌웨어 안정화 대기(NPU 패스당 약 49 µs) 포함 — 에너지 최대 약 7 µJ 과대(측정값에서 빼지 않음). 같은 대기를 넣으면 NPU 전처리 (Gabor 필터뱅크) 는 1.95 ms.</t>
         </is>
       </c>
     </row>
@@ -1622,7 +1622,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.840</t>
+          <t>0.704</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1642,37 +1642,37 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>data/logs-local/board_v4d_fe_oldfw.log</t>
+          <t>data/logs-local/board_v4d_fe_oldfw.log (CPU 몫 -0.136 ms 환산: data/logs-local/board_v4d_fe_log32.log)</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>74</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>52</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>40 ~ 78</t>
+          <t>39 ~ 74</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.678</t>
+          <t>1.406</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1752,37 +1752,37 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>data/logs-local/board_v4d_fe_b64.log</t>
+          <t>data/logs-local/board_v4d_fe_b64.log (CPU 몫 -0.272 ms 환산: data/logs-local/board_v4d_fe_b64_log32.log)</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>77</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>145</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>98</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>80 ~ 152</t>
+          <t>77 ~ 145</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1842,7 +1842,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.661</t>
+          <t>1.391</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1862,37 +1862,37 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>data/logs-local/board_v4d_fe_f31.log</t>
+          <t>data/logs-local/board_v4d_fe_f31.log (CPU 몫 -0.270 ms 환산: data/logs-local/board_v4d_fe_f31_log32.log)</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>71</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>136</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>93</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>74 ~ 142</t>
+          <t>71 ~ 136</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>3.319</t>
+          <t>2.782</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1972,37 +1972,37 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>6.49</t>
+          <t>5.96</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>data/logs-local/board_v4d_fe_b64f31.log</t>
+          <t>data/logs-local/board_v4d_fe_b64f31.log (CPU 몫 -0.537 ms 환산: data/logs-local/board_v4d_fe_b64f31_log32.log)</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>133</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>252</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>172</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>139 ~ 265</t>
+          <t>133 ~ 252</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -3684,7 +3684,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1.371</t>
+          <t>1.235</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -3704,32 +3704,32 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>r &gt; 0.33</t>
+          <t>r &gt; 0.17</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>r = 4.59; E_X 40 / E_Y 71 µJ → 성립</t>
+          <t>r = 4.59; E_X 39 / E_Y 71 µJ → 성립</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>r = 2.89; E_X 78 / E_Y 130 µJ → 성립</t>
+          <t>r = 2.89; E_X 74 / E_Y 130 µJ → 성립</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>r = 1.44; E_X 56 / E_Y 78 µJ → 성립</t>
+          <t>r = 1.44; E_X 52 / E_Y 78 µJ → 성립</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>r = 19.07; E_X 119 / E_Y 256 µJ → 성립</t>
+          <t>r = 19.07; E_X 118 / E_Y 256 µJ → 성립</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1.371</t>
+          <t>1.235</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -3766,32 +3766,32 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>r &lt; 12.7</t>
+          <t>r &lt; 14.4</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>12.73</t>
+          <t>14.41</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>r = 4.59; E_X 40 / E_Y 43 µJ → 성립</t>
+          <t>r = 4.59; E_X 39 / E_Y 43 µJ → 성립</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>r = 2.89; E_X 78 / E_Y 98 µJ → 성립</t>
+          <t>r = 2.89; E_X 74 / E_Y 98 µJ → 성립</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>r = 1.44; E_X 56 / E_Y 78 µJ → 성립</t>
+          <t>r = 1.44; E_X 52 / E_Y 78 µJ → 성립</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>r = 19.07; E_X 119 / E_Y 112 µJ → 불성립</t>
+          <t>r = 19.07; E_X 118 / E_Y 112 µJ → 불성립</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
